--- a/excel/universities/university-of-helsinki.xlsx
+++ b/excel/universities/university-of-helsinki.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,27 +125,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">Application period for autumn 2026 ran from 2026-01-02 to 2026-01-16.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,37 +229,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-23; admissions results published between 2026-04-01 and 2026-04-15.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +333,156 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload official educational documents in the application form.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final transcript required for all applicants; latest transcript if degree incomplete.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English proficiency document required unless exempt.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/application-attachments</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific attachments</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programmes may require motivation letter CV or other materials.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/how-apply-to-international-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +546,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -442,55 +583,147 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Department of Computer Science</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Jukka K Nurminen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Professor of Computer Science</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research portal profile text</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hannu Toivonen</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Professor</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data science; Computational creativity; Data mining</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000+</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60+</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research group page</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/researchgroups/computational-creativity-and-data-mining/people/hannu-toivonen</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.helsinki.fi/</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Citation count and h-index are stated on the official research group page as Google Scholar-based approximations.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>

--- a/excel/universities/university-of-helsinki.xlsx
+++ b/excel/universities/university-of-helsinki.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -495,7 +496,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,70 +507,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">department_name</t>
+          <t xml:space="preserve">unit_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">professor_name</t>
+          <t xml:space="preserve">unit_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">parent_unit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_areas</t>
+          <t xml:space="preserve">campus_or_city</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">researchgate_url</t>
+          <t xml:space="preserve">focus_areas</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">google_scholar_url</t>
+          <t xml:space="preserve">official_url</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation_count</t>
+          <t xml:space="preserve">notes</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">h_index</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_source</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_last_checked</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">official_profile_url</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">email</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">notes</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -583,70 +554,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Computer Science</t>
+          <t xml:space="preserve">Faculty</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jukka K Nurminen</t>
+          <t xml:space="preserve">Faculty of Agriculture and Forestry</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor of Computer Science</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+          <t xml:space="preserve">Helsinki</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Agriculture; Forestry; Food sciences</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-agriculture-and-forestry</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official university faculty page.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Helsinki research portal profile text</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -660,70 +601,1063 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Arts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arts</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-arts</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biological and Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biology; Environmental sciences</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-biological-and-environmental-sciences</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biological and Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environmental sciences</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-biological-and-environmental-sciences</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department listed on official faculty organization page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Educational Sciences</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-educational-sciences</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Law</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-law</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-medicine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmacy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-pharmacy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science; Physics; Mathematics; Chemistry</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Department of Computer Science</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-computer-science</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Physics</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-physics</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Chemistry</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemistry</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-chemistry</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Geosciences and Geography</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geosciences; Geography</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-geosciences-and-geography</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Statistics</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-mathematics-and-statistics</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Theology</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theology</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-theology</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veterinary medicine</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-veterinary-medicine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">professor_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research_areas</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">researchgate_url</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google_scholar_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h_index</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_profile_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jukka K Nurminen</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor of Computer Science</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research portal profile text</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Mikko Koivisto</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Algorithms; Probabilistic inference; Artificial intelligence; Combinatorics</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/people/mikko-koivisto</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official University of Helsinki profile used for title and research areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hannu Toivonen</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Professor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Artificial intelligence; Data science; Computational creativity; Data mining</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">28000+</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">60+</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t xml:space="preserve">University of Helsinki research group page</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.helsinki.fi/en/researchgroups/computational-creativity-and-data-mining/people/hannu-toivonen</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Citation count and h-index are stated on the official research group page as Google Scholar-based approximations.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
